--- a/Test upload format/MSME/MSME_D1.xlsx
+++ b/Test upload format/MSME/MSME_D1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>CGPAN</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>QAMSME20</t>
+  </si>
+  <si>
+    <t>01-10-2026</t>
   </si>
   <si>
     <t>CGMSMGEN2109202600357115</t>
@@ -165,12 +168,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -358,12 +360,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -697,7 +705,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -721,16 +729,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -739,85 +747,85 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
@@ -846,7 +854,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,8 +1124,7 @@
     <col min="2" max="2" width="28.5714285714286" style="3" customWidth="1"/>
     <col min="3" max="3" width="28.7142857142857" style="3" customWidth="1"/>
     <col min="4" max="4" width="26.5714285714286" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.2857142857143" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="12.6666666666667" style="3"/>
+    <col min="5" max="16384" width="12.6666666666667" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
@@ -1144,274 +1151,274 @@
       <c r="C2" s="8">
         <v>10000</v>
       </c>
-      <c r="D2" s="9">
-        <v>46305</v>
+      <c r="D2" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="8">
         <v>20000</v>
       </c>
-      <c r="D3" s="9">
-        <v>46305</v>
+      <c r="D3" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8">
         <v>30000</v>
       </c>
-      <c r="D4" s="9">
-        <v>46305</v>
+      <c r="D4" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="15" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8">
         <v>40000</v>
       </c>
-      <c r="D5" s="9">
-        <v>46305</v>
+      <c r="D5" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="8">
         <v>50000</v>
       </c>
-      <c r="D6" s="9">
-        <v>46305</v>
+      <c r="D6" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="8">
         <v>60000</v>
       </c>
-      <c r="D7" s="9">
-        <v>46305</v>
+      <c r="D7" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="8">
         <v>70000</v>
       </c>
-      <c r="D8" s="9">
-        <v>46305</v>
+      <c r="D8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="8">
         <v>80000</v>
       </c>
-      <c r="D9" s="9">
-        <v>46305</v>
+      <c r="D9" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="8">
         <v>90000</v>
       </c>
-      <c r="D10" s="9">
-        <v>46305</v>
+      <c r="D10" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:4">
       <c r="A11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="8">
         <v>100000</v>
       </c>
-      <c r="D11" s="9">
-        <v>46305</v>
+      <c r="D11" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
       <c r="A12" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="8">
         <v>110000</v>
       </c>
-      <c r="D12" s="9">
-        <v>46305</v>
+      <c r="D12" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:4">
       <c r="A13" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="8">
         <v>120000</v>
       </c>
-      <c r="D13" s="9">
-        <v>46305</v>
+      <c r="D13" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:4">
       <c r="A14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="8">
         <v>130000</v>
       </c>
-      <c r="D14" s="9">
-        <v>46305</v>
+      <c r="D14" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:4">
       <c r="A15" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="8">
         <v>140000</v>
       </c>
-      <c r="D15" s="9">
-        <v>46305</v>
+      <c r="D15" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:4">
       <c r="A16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="8">
         <v>150000</v>
       </c>
-      <c r="D16" s="9">
-        <v>46305</v>
+      <c r="D16" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:4">
       <c r="A17" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="8">
         <v>160000</v>
       </c>
-      <c r="D17" s="9">
-        <v>46305</v>
+      <c r="D17" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="8">
         <v>170000</v>
       </c>
-      <c r="D18" s="9">
-        <v>46305</v>
+      <c r="D18" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:4">
       <c r="A19" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="8">
         <v>180000</v>
       </c>
-      <c r="D19" s="9">
-        <v>46305</v>
+      <c r="D19" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="8">
         <v>190000</v>
       </c>
-      <c r="D20" s="9">
-        <v>46305</v>
+      <c r="D20" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="8">
         <v>200000</v>
       </c>
-      <c r="D21" s="9">
-        <v>46305</v>
+      <c r="D21" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Test upload format/MSME/MSME_D1.xlsx
+++ b/Test upload format/MSME/MSME_D1.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk Upload Coloumns" sheetId="1" r:id="rId1"/>

--- a/Test upload format/MSME/MSME_D1.xlsx
+++ b/Test upload format/MSME/MSME_D1.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk Upload Coloumns" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
     <t>CGPAN</t>
   </si>
@@ -41,127 +41,172 @@
     <t>DisbursementDate</t>
   </si>
   <si>
-    <t>CGMSMGEN2109202600357114</t>
-  </si>
-  <si>
-    <t>QAMSME20</t>
-  </si>
-  <si>
-    <t>01-10-2026</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357115</t>
-  </si>
-  <si>
-    <t>QAMSME19</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357116</t>
-  </si>
-  <si>
-    <t>QAMSME18</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357117</t>
-  </si>
-  <si>
-    <t>QAMSME17</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357118</t>
-  </si>
-  <si>
-    <t>QAMSME16</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357119</t>
-  </si>
-  <si>
-    <t>QAMSME15</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357120</t>
-  </si>
-  <si>
-    <t>QAMSME14</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357121</t>
-  </si>
-  <si>
-    <t>QAMSME13</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357122</t>
-  </si>
-  <si>
-    <t>QAMSME12</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357123</t>
-  </si>
-  <si>
-    <t>QAMSME11</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357124</t>
-  </si>
-  <si>
-    <t>QAMSME10</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357125</t>
-  </si>
-  <si>
-    <t>QAMSME09</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357126</t>
-  </si>
-  <si>
-    <t>QAMSME08</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357127</t>
-  </si>
-  <si>
-    <t>QAMSME07</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357128</t>
-  </si>
-  <si>
-    <t>QAMSME06</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357129</t>
-  </si>
-  <si>
-    <t>QAMSME05</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357130</t>
-  </si>
-  <si>
-    <t>QAMSME04</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357131</t>
-  </si>
-  <si>
-    <t>QAMSME03</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357132</t>
-  </si>
-  <si>
-    <t>QAMSME02</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357133</t>
-  </si>
-  <si>
-    <t>QAMSME01</t>
+    <t>CGMSMGEN2209202600357192</t>
+  </si>
+  <si>
+    <t>Aloan01</t>
+  </si>
+  <si>
+    <t>200000000</t>
+  </si>
+  <si>
+    <t>15-09-2026</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357193</t>
+  </si>
+  <si>
+    <t>Aloan02</t>
+  </si>
+  <si>
+    <t>500000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357194</t>
+  </si>
+  <si>
+    <t>Aloan03</t>
+  </si>
+  <si>
+    <t>300000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357195</t>
+  </si>
+  <si>
+    <t>Aloan04</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357196</t>
+  </si>
+  <si>
+    <t>Aloan05</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357197</t>
+  </si>
+  <si>
+    <t>Aloan06</t>
+  </si>
+  <si>
+    <t>460000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357198</t>
+  </si>
+  <si>
+    <t>Aloan07</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357199</t>
+  </si>
+  <si>
+    <t>Aloan08</t>
+  </si>
+  <si>
+    <t>90000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357200</t>
+  </si>
+  <si>
+    <t>Aloan09</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357201</t>
+  </si>
+  <si>
+    <t>Aloan10</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357202</t>
+  </si>
+  <si>
+    <t>Aloan11</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357203</t>
+  </si>
+  <si>
+    <t>Aloan12</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357204</t>
+  </si>
+  <si>
+    <t>Aloan13</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357205</t>
+  </si>
+  <si>
+    <t>Aloan14</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357206</t>
+  </si>
+  <si>
+    <t>Aloan15</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357207</t>
+  </si>
+  <si>
+    <t>Aloan16</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357208</t>
+  </si>
+  <si>
+    <t>Aloan17</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357209</t>
+  </si>
+  <si>
+    <t>Aloan18</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357210</t>
+  </si>
+  <si>
+    <t>Aloan19</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357211</t>
+  </si>
+  <si>
+    <t>Aloan20</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357212</t>
+  </si>
+  <si>
+    <t>Aloan21</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357213</t>
+  </si>
+  <si>
+    <t>Aloan22</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357214</t>
+  </si>
+  <si>
+    <t>Aloan23</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2209202600357215</t>
+  </si>
+  <si>
+    <t>Aloan24</t>
   </si>
 </sst>
 </file>
@@ -198,8 +243,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;Aptos Narrow&quot;"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -369,7 +414,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -580,6 +625,17 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,7 +761,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,34 +773,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -850,11 +906,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,7 +1171,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.7142857142857" style="3" customWidth="1"/>
@@ -1145,280 +1199,336 @@
       <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8">
-        <v>10000</v>
+      <c r="C2" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8">
-        <v>20000</v>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="8">
-        <v>30000</v>
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="15" spans="1:4">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8">
-        <v>40000</v>
+      <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="8">
-        <v>50000</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:4">
-      <c r="A7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="8">
-        <v>60000</v>
+      <c r="A7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="8">
-        <v>70000</v>
+        <v>21</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="8">
-        <v>80000</v>
+        <v>24</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="8">
-        <v>90000</v>
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:4">
+      <c r="A11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:4">
+      <c r="A12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:4">
+      <c r="A13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:4">
+      <c r="A14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" ht="15" spans="1:4">
-      <c r="A11" s="7" t="s">
+      <c r="D14" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:4">
+      <c r="A15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:4">
+      <c r="A16" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:4">
+      <c r="A17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:4">
+      <c r="A18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:4">
+      <c r="A19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:4">
+      <c r="A20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="8">
-        <v>100000</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:4">
-      <c r="A12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="D20" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:4">
+      <c r="A21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8">
-        <v>110000</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:4">
-      <c r="A13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="8">
-        <v>120000</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:4">
-      <c r="A14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="8">
-        <v>130000</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:4">
-      <c r="A15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="8">
-        <v>140000</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:4">
-      <c r="A16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="8">
-        <v>150000</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:4">
-      <c r="A17" s="7" t="s">
+      <c r="D21" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:4">
+      <c r="A22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:4">
+      <c r="A23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:4">
+      <c r="A24" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:4">
+      <c r="A25" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="8">
-        <v>160000</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="1:4">
-      <c r="A18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="8">
-        <v>170000</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:4">
-      <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="8">
-        <v>180000</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:4">
-      <c r="A20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="8">
-        <v>190000</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:4">
-      <c r="A21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="8">
-        <v>200000</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>6</v>
+      <c r="D25" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
